--- a/data/trans_orig/KC10IN_T-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/KC10IN_T-Provincia-trans_orig.xlsx
@@ -489,7 +489,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>KIDSCREEN autopercibido (escala)</t>
+          <t>KIDSCREEN autopercibido (escala) (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -538,7 +538,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -581,14 +581,14 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>48,29; 55,07</t>
+          <t>49,07; 55,07</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -621,24 +621,24 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>53,4; 64,28</t>
+          <t>53,14; 64,4</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>57,57; 68,37</t>
+          <t>57,59; 68,24</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>55,43; 64,71</t>
+          <t>55,79; 64,86</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -671,17 +671,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>56,04; 63,16</t>
+          <t>55,89; 63,79</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>56,23; 64,11</t>
+          <t>55,98; 64,28</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>57,07; 62,42</t>
+          <t>57,11; 62,59</t>
         </is>
       </c>
     </row>
@@ -721,17 +721,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>48,53; 70,59</t>
+          <t>48,95; 71,51</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>58,28; 82,15</t>
+          <t>58,44; 82,11</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>58,15; 81,78</t>
+          <t>58,29; 81,58</t>
         </is>
       </c>
     </row>
@@ -771,24 +771,24 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>60,92; 69,97</t>
+          <t>60,59; 69,44</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>56,38; 63,61</t>
+          <t>56,44; 64,03</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>59,12; 64,8</t>
+          <t>59,06; 64,85</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -821,24 +821,24 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>53,8; 59,21</t>
+          <t>53,94; 59,28</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>53,4; 61,41</t>
+          <t>53,49; 61,76</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>54,44; 59,58</t>
+          <t>54,41; 59,48</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -871,17 +871,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>55,44; 62,59</t>
+          <t>55,68; 62,79</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>55,85; 63,1</t>
+          <t>56,0; 63,01</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>56,5; 61,68</t>
+          <t>56,17; 61,27</t>
         </is>
       </c>
     </row>
@@ -921,17 +921,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>52,58; 55,54</t>
+          <t>52,57; 55,5</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>52,3; 55,48</t>
+          <t>52,31; 55,54</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>52,77; 54,84</t>
+          <t>52,7; 54,96</t>
         </is>
       </c>
     </row>
@@ -971,17 +971,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>55,24; 58,75</t>
+          <t>55,03; 58,74</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>57,44; 63,15</t>
+          <t>57,44; 62,69</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>56,9; 60,29</t>
+          <t>57,0; 60,47</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/KC10IN_T-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/KC10IN_T-Provincia-trans_orig.xlsx
@@ -621,17 +621,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>53,14; 64,4</t>
+          <t>53,33; 64,11</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>57,59; 68,24</t>
+          <t>58,03; 67,88</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>55,79; 64,86</t>
+          <t>55,66; 64,49</t>
         </is>
       </c>
     </row>
@@ -671,17 +671,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>55,89; 63,79</t>
+          <t>56,06; 63,81</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>55,98; 64,28</t>
+          <t>56,49; 63,98</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>57,11; 62,59</t>
+          <t>56,87; 62,51</t>
         </is>
       </c>
     </row>
@@ -721,17 +721,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>48,95; 71,51</t>
+          <t>48,95; 70,59</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>58,44; 82,11</t>
+          <t>58,45; 82,34</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>58,29; 81,58</t>
+          <t>58,41; 81,58</t>
         </is>
       </c>
     </row>
@@ -771,17 +771,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>60,59; 69,44</t>
+          <t>61,01; 69,31</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>56,44; 64,03</t>
+          <t>56,07; 63,72</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>59,06; 64,85</t>
+          <t>59,42; 64,97</t>
         </is>
       </c>
     </row>
@@ -821,17 +821,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>53,94; 59,28</t>
+          <t>53,74; 59,22</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>53,49; 61,76</t>
+          <t>53,47; 61,91</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>54,41; 59,48</t>
+          <t>54,25; 59,54</t>
         </is>
       </c>
     </row>
@@ -871,17 +871,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>55,68; 62,79</t>
+          <t>55,42; 62,56</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>56,0; 63,01</t>
+          <t>55,77; 62,49</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>56,17; 61,27</t>
+          <t>56,36; 61,71</t>
         </is>
       </c>
     </row>
@@ -921,17 +921,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>52,57; 55,5</t>
+          <t>52,55; 55,32</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>52,31; 55,54</t>
+          <t>52,28; 55,39</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>52,7; 54,96</t>
+          <t>52,85; 55,0</t>
         </is>
       </c>
     </row>
@@ -971,17 +971,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>55,03; 58,74</t>
+          <t>55,01; 58,64</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>57,44; 62,69</t>
+          <t>57,3; 62,15</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>57,0; 60,47</t>
+          <t>57,09; 60,49</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/KC10IN_T-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/KC10IN_T-Provincia-trans_orig.xlsx
@@ -495,12 +495,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -548,17 +548,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>53,47</t>
+          <t>48,29</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>48,29</t>
+          <t>53,41</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>51,47</t>
+          <t>51,54</t>
         </is>
       </c>
     </row>
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
           <t>51,36; 55,07</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>49,07; 55,07</t>
+          <t>48,29; 54,0</t>
         </is>
       </c>
     </row>
@@ -598,17 +598,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>57,9</t>
+          <t>63,25</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>62,96</t>
+          <t>62,4</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>60,36</t>
+          <t>62,9</t>
         </is>
       </c>
     </row>
@@ -621,17 +621,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>53,33; 64,11</t>
+          <t>58,12; 68,49</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>58,03; 67,88</t>
+          <t>58,99; 66,24</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>55,66; 64,49</t>
+          <t>59,41; 66,25</t>
         </is>
       </c>
     </row>
@@ -648,17 +648,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>59,29</t>
+          <t>59,9</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>59,95</t>
+          <t>59,17</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>59,64</t>
+          <t>59,54</t>
         </is>
       </c>
     </row>
@@ -671,17 +671,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>56,06; 63,81</t>
+          <t>56,29; 64,09</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>56,49; 63,98</t>
+          <t>55,94; 63,08</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>56,87; 62,51</t>
+          <t>57,05; 62,35</t>
         </is>
       </c>
     </row>
@@ -698,17 +698,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>59,38</t>
+          <t>71,94</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>73,34</t>
+          <t>59,12</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>71,68</t>
+          <t>70,09</t>
         </is>
       </c>
     </row>
@@ -721,17 +721,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>48,95; 70,59</t>
+          <t>58,15; 81,74</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>58,45; 82,34</t>
+          <t>49,19; 70,49</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>58,41; 81,58</t>
+          <t>57,99; 81,07</t>
         </is>
       </c>
     </row>
@@ -748,17 +748,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>64,82</t>
+          <t>60,01</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>59,88</t>
+          <t>64,8</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>61,97</t>
+          <t>62,09</t>
         </is>
       </c>
     </row>
@@ -771,17 +771,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>61,01; 69,31</t>
+          <t>56,46; 63,67</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>56,07; 63,72</t>
+          <t>60,86; 70,01</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>59,42; 64,97</t>
+          <t>59,28; 64,97</t>
         </is>
       </c>
     </row>
@@ -798,17 +798,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>56,34</t>
+          <t>56,73</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>56,92</t>
+          <t>56,23</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>56,66</t>
+          <t>56,48</t>
         </is>
       </c>
     </row>
@@ -821,17 +821,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>53,74; 59,22</t>
+          <t>53,07; 61,51</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>53,47; 61,91</t>
+          <t>53,77; 58,97</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>54,25; 59,54</t>
+          <t>54,27; 59,29</t>
         </is>
       </c>
     </row>
@@ -848,17 +848,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>58,77</t>
+          <t>58,85</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>58,96</t>
+          <t>58,72</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>58,89</t>
+          <t>58,8</t>
         </is>
       </c>
     </row>
@@ -871,17 +871,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>55,42; 62,56</t>
+          <t>55,65; 62,86</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>55,77; 62,49</t>
+          <t>55,56; 62,55</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>56,36; 61,71</t>
+          <t>56,44; 61,63</t>
         </is>
       </c>
     </row>
@@ -898,17 +898,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>53,88</t>
+          <t>53,76</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>53,67</t>
+          <t>53,82</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>53,76</t>
+          <t>53,78</t>
         </is>
       </c>
     </row>
@@ -921,17 +921,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>52,55; 55,32</t>
+          <t>52,39; 55,55</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>52,28; 55,39</t>
+          <t>52,51; 55,48</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>52,85; 55,0</t>
+          <t>52,79; 54,89</t>
         </is>
       </c>
     </row>
@@ -948,17 +948,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>57,28</t>
+          <t>58,93</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>59,24</t>
+          <t>57,94</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>58,38</t>
+          <t>58,51</t>
         </is>
       </c>
     </row>
@@ -971,17 +971,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>55,01; 58,64</t>
+          <t>57,29; 62,02</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>57,3; 62,15</t>
+          <t>56,75; 59,14</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>57,09; 60,49</t>
+          <t>57,36; 60,14</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/KC10IN_T-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/KC10IN_T-Provincia-trans_orig.xlsx
@@ -16,7 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -97,7 +99,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -110,6 +112,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -476,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -489,7 +494,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>KIDSCREEN autopercibido (escala) (tasa de respuesta: 100,0%)</t>
+          <t>KIDSCREEN autopercibido (escala) (tasa de respuesta: 29,74%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -546,149 +551,105 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>48,29</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>53,41</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>51,54</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>48.28975497451077</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>53.40849620609651</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>51.54461499461731</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>51,36; 55,07</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>48,29; 54,0</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr"/>
+      <c r="D5" s="5" t="n">
+        <v>51.35620108921714</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>48.28975497451076</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr"/>
+      <c r="D6" s="5" t="n">
+        <v>55.07076042059646</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>54.00005903484307</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Cádiz</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>63,25</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>62,4</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>62,9</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>58,12; 68,49</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>58,99; 66,24</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>59,41; 66,25</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>63.2521167301708</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>62.40243810442747</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>62.90474713637129</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Córdoba</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>59,9</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>59,17</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>59,54</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>58.12107922304056</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>58.98859388106875</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>59.40986005651976</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>56,29; 64,09</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>55,94; 63,08</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>57,05; 62,35</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>68.48552782570908</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>66.2365311935062</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>66.25454116631538</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Granada</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -696,149 +657,109 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>71,94</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>59,12</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>70,09</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>59.90232314086748</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>59.17202165385864</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>59.53699374287311</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>58,15; 81,74</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>49,19; 70,49</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>57,99; 81,07</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>56.2920153467678</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>55.93965284233474</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>57.04614374596856</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Huelva</t>
-        </is>
-      </c>
+      <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>64.09311331004888</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>63.07565042712198</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>62.34558030305751</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>60,01</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>64,8</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>62,09</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>56,46; 63,67</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>60,86; 70,01</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>59,28; 64,97</t>
-        </is>
+      <c r="C13" s="5" t="n">
+        <v>71.93901219386224</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>59.12032301285595</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>70.09005483261924</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>Jaén</t>
-        </is>
-      </c>
+      <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>56,73</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>56,23</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>56,48</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>58.14758193050756</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>49.18927080047467</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>57.98967471276728</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>53,07; 61,51</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>53,77; 58,97</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>54,27; 59,29</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>81.74469448553337</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>70.48859315273698</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>81.07106315871769</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Málaga</t>
+          <t>Huelva</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -846,147 +767,272 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>58,85</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>58,72</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>58,8</t>
-        </is>
+      <c r="C16" s="5" t="n">
+        <v>60.01336870400376</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>64.79738534351647</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>62.09107609019584</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>55,65; 62,86</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>55,56; 62,55</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>56,44; 61,63</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>56.46204829323229</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>60.85960420102526</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>59.28470601923297</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>Sevilla</t>
-        </is>
-      </c>
+      <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>63.67380377502681</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>70.0124899214061</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>64.96609990435925</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Jaén</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>53,76</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>53,82</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>53,78</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="n"/>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>52,39; 55,55</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>52,51; 55,48</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>52,79; 54,89</t>
-        </is>
+      <c r="C19" s="5" t="n">
+        <v>56.72739475008906</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>56.22933771368758</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>56.48411741443437</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
+      <c r="A20" s="1" t="n"/>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>58,93</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>57,94</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>58,51</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>53.06674028346981</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>53.77052662284122</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>54.26784104925336</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n"/>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>57,29; 62,02</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>56,75; 59,14</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>57,36; 60,14</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>61.51485894373445</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>58.97349764996302</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>59.28789965388958</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>58.84700776830589</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>58.72201749819194</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>58.79926047933979</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>55.65131212272277</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>55.56436076655433</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>56.43584022950439</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>62.85783347198037</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>62.54930913596905</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>61.62769160427359</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="n">
+        <v>53.75503162385034</v>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>53.81675377004372</v>
+      </c>
+      <c r="E25" s="5" t="n">
+        <v>53.78259289128557</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="n">
+        <v>52.38876967621584</v>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>52.50540007040587</v>
+      </c>
+      <c r="E26" s="5" t="n">
+        <v>52.78702770682737</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="n">
+        <v>55.54953516762339</v>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>55.48382339373891</v>
+      </c>
+      <c r="E27" s="5" t="n">
+        <v>54.88763771704121</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="n">
+        <v>58.92573356494936</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>57.93558560135788</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>58.50662137489838</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="n">
+        <v>57.28806576354001</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>56.74706226701043</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>57.3591037734431</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="n">
+        <v>62.02226257352562</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>59.1375121271623</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>60.13804743013878</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -994,16 +1040,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A19:A21"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
